--- a/AAII_Financials/Quarterly/ALGM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALGM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>ALGM</t>
   </si>
@@ -656,442 +656,455 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46199</v>
+      </c>
+      <c r="E7" s="2">
         <v>46108</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46017</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45835</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45744</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45653</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45380</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45289</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44918</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44827</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44736</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44645</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44554</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44463</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44372</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44099</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43917</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43644</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>39353</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>39262</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>39171</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>39080</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>38989</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>259200</v>
+      </c>
+      <c r="E8" s="3">
         <v>243200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>229200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>214300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>203400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>192800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>177900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>187400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>166900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>240600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>255000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>275500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>278300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>269400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>248800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>237700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>217800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>200300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>186600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>193600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>188100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>175100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>164400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>136600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>115000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>650100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>152400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>79700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>78700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>79300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>80200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>82500</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>133600</v>
+      </c>
+      <c r="E9" s="3">
         <v>127100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>122100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>115000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>112100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>111600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>96700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>101700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>92100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>117300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>121200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>116000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>120300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>116400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>106200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>105600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>99400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>90700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>85500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>91100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>94000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>88100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>90000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>74900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>59300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>388800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>93100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>53700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>53900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>51300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>52700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>52900</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>125600</v>
+      </c>
+      <c r="E10" s="3">
         <v>116100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>107100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>99300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>91300</v>
-      </c>
-      <c r="H10" s="3">
-        <v>81200</v>
       </c>
       <c r="I10" s="3">
         <v>81200</v>
       </c>
       <c r="J10" s="3">
+        <v>81200</v>
+      </c>
+      <c r="K10" s="3">
         <v>85700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>74800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>123200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>133800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>159500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>158000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>153100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>142600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>132100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>118400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>109600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>101100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>102500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>94100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>87000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>74400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>61700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>55700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>261300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>59300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>26000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>24800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>28000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>27500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1126,106 +1139,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>55200</v>
+      </c>
+      <c r="E12" s="3">
         <v>50800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>52900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>50900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>46500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>45000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>43300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>43500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>45200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>45800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>44400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>43400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>43000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>41800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>39600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>35600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>33700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>32400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>30300</v>
-      </c>
-      <c r="V12" s="3">
-        <v>29600</v>
       </c>
       <c r="W12" s="3">
         <v>29600</v>
       </c>
       <c r="X12" s="3">
+        <v>29600</v>
+      </c>
+      <c r="Y12" s="3">
         <v>28100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>31000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>25100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>24400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>102100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>26100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>10700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>10600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>10500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>9500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>9300</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1322,17 +1339,20 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E14" s="3">
         <v>18300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1340,62 +1360,62 @@
         <v>11</v>
       </c>
       <c r="H14" s="3">
+        <v>800</v>
+      </c>
+      <c r="I14" s="3">
         <v>6500</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M14" s="3">
         <v>9600</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T14" s="3">
         <v>6100</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>11</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y14" s="3">
         <v>7100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>9100</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1411,8 +1431,8 @@
       <c r="AE14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1420,62 +1440,65 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E15" s="3">
         <v>17800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>17000</v>
       </c>
       <c r="F15" s="3">
         <v>17000</v>
       </c>
       <c r="G15" s="3">
-        <v>15900</v>
+        <v>17000</v>
       </c>
       <c r="H15" s="3">
         <v>15900</v>
       </c>
       <c r="I15" s="3">
+        <v>15900</v>
+      </c>
+      <c r="J15" s="3">
         <v>16100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>16300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>20200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>15100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>14300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>14100</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
       <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
         <v>100</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
-      </c>
       <c r="U15" s="3">
         <v>0</v>
       </c>
@@ -1486,11 +1509,11 @@
         <v>0</v>
       </c>
       <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
         <v>100</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
-      </c>
       <c r="Z15" s="3">
         <v>0</v>
       </c>
@@ -1498,13 +1521,13 @@
         <v>0</v>
       </c>
       <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
         <v>100</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="3" t="s">
-        <v>11</v>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>11</v>
@@ -1518,8 +1541,11 @@
       <c r="AH15" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1577,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>233800</v>
+      </c>
+      <c r="E17" s="3">
         <v>217800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>219600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>208100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>206100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>199500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>177900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>183300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>177500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>203200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>218300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>202600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>207500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>210100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>183200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>177800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>203000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>170000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>151000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>155100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>155900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>155700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>197700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>124200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>110500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>597300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>144700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>75400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>75800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>73700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>73400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E18" s="3">
         <v>25400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6700</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>4100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>37300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>36700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>72900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>70700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>59300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>65600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>59900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>14800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>30300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>35600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>38500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>32200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>19400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-33300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>12400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>52800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>7700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>5600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,190 +1816,194 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
         <v>4800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
+        <v>37200</v>
+      </c>
+      <c r="L20" s="3">
         <v>1100</v>
       </c>
-      <c r="H20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>37200</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
+        <v>5700</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R20" s="3">
+        <v>6500</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="W20" s="3">
+        <v>800</v>
+      </c>
+      <c r="X20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AE20" s="3">
         <v>1100</v>
       </c>
-      <c r="L20" s="3">
-        <v>5700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>2700</v>
-      </c>
-      <c r="P20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>6500</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-800</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>3700</v>
-      </c>
-      <c r="V20" s="3">
-        <v>800</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>900</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>400</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>2900</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>41500</v>
+      </c>
+      <c r="E21" s="3">
         <v>38300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>22300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19800</v>
       </c>
-      <c r="G21" s="3">
-        <v>12000</v>
-      </c>
       <c r="H21" s="3">
+        <v>12800</v>
+      </c>
+      <c r="I21" s="3">
         <v>10600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>15900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>53500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>59600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>88100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>82300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>70900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>84700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>71300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>24200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>42200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>51300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>51700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>44100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>29100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-23400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>24200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>16900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>117300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>26100</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>11</v>
       </c>
@@ -1976,46 +2013,49 @@
       <c r="AG21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI21" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E22" s="3">
         <v>5100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>5400</v>
       </c>
       <c r="L22" s="3">
         <v>5400</v>
       </c>
       <c r="M22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="N22" s="3">
         <v>3900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>800</v>
       </c>
       <c r="O22" s="3">
         <v>800</v>
@@ -2023,8 +2063,8 @@
       <c r="P22" s="3">
         <v>800</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>11</v>
+      <c r="Q22" s="3">
+        <v>800</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>11</v>
@@ -2038,14 +2078,14 @@
       <c r="U22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>11</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>11</v>
@@ -2062,219 +2102,228 @@
       <c r="AC22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE22" s="3">
         <v>300</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>400</v>
       </c>
       <c r="AF22" s="3">
         <v>400</v>
       </c>
       <c r="AG22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AH22" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-43100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>17300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>36400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>73100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>68100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>67900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>72100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>59100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>12200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>30200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>39300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>39400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>32000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>17100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-35600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>11700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>53300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>6400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E24" s="3">
         <v>13700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-7900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-9300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-9500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>24300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-30500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>16200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1600</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>900</v>
       </c>
       <c r="AF24" s="3">
         <v>900</v>
       </c>
       <c r="AG24" s="3">
+        <v>900</v>
+      </c>
+      <c r="AH24" s="3">
         <v>300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2420,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-33600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>33400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>65700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>60900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>62000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>64600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>50600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>25700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>33000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>33200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>27700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>8700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>9600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>37100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-33700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>33300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>65600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>60900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>62000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>64500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>50600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>25600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>32900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>33200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>27700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>8600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>9600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>37000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2723,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,8 +2824,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2925,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3026,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-37200</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1100</v>
       </c>
-      <c r="H32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-37200</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="N32" s="3">
+        <v>2700</v>
+      </c>
+      <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="S32" s="3">
+        <v>800</v>
+      </c>
+      <c r="T32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="U32" s="3">
+        <v>100</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="X32" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-1100</v>
       </c>
-      <c r="L32" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>2700</v>
-      </c>
-      <c r="N32" s="3">
-        <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="R32" s="3">
-        <v>800</v>
-      </c>
-      <c r="S32" s="3">
-        <v>2500</v>
-      </c>
-      <c r="T32" s="3">
-        <v>100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="W32" s="3">
-        <v>200</v>
-      </c>
-      <c r="X32" s="3">
-        <v>2400</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>700</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-33700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>33300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>65600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>60900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>62000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>64500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>50600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>25600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>32900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>33200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>27700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>8600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>9600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>37000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3329,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-33700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>33300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>65600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>60900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>62000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>64500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>50600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>25600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>32900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>33200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>27700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>8600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>9600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>37000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46199</v>
+      </c>
+      <c r="E38" s="2">
         <v>46108</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46017</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45835</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45744</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45653</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45380</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45289</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44918</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44827</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44736</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44645</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44554</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44463</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44372</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44099</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43917</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43644</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>39353</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>39262</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>39171</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>39080</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>38989</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3575,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,86 +3612,87 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E41" s="3">
         <v>168800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>155200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>117500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>129100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>121300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>138500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>188800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>173100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>212100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>214300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>370000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>353400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>351600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>334300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>293600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>286600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>282400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>259200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>248600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>221900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>197200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>157700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>202000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>215600</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>11</v>
       </c>
@@ -3624,8 +3711,11 @@
       <c r="AH41" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3663,11 +3753,11 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>5200</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -3722,86 +3812,89 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>110900</v>
+      </c>
+      <c r="E43" s="3">
         <v>115000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>99700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>105800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>89400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>87200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>83800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>77000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>67100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>122300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>118200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>123400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>125400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>130500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>134200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>124500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>125000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>120700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>107400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>99100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>103100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>94800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>88900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>77500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>74600</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>11</v>
       </c>
@@ -3820,86 +3913,89 @@
       <c r="AH43" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>188100</v>
+      </c>
+      <c r="E44" s="3">
         <v>181800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>178200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>170700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>173800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>183900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>193100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>176600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>175900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>162300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>165600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>173100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>174200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>151300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>119600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>98400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>88900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>86200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>78900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>78000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>82400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>87500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>94000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>104800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>108400</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>11</v>
       </c>
@@ -3918,86 +4014,89 @@
       <c r="AH44" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>17500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>53200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>36000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>38600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31900</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>11</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>31900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>28900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>28600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>20200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>45100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>51000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>38000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>22900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>11800</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>11</v>
       </c>
@@ -4016,86 +4115,89 @@
       <c r="AH45" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>508000</v>
+      </c>
+      <c r="E46" s="3">
         <v>503600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>515400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>469500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>447100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>483000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>495600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>523600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>490300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>572200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>549500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>714900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>700300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>665800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>620000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>545500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>529000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>511700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>469200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>445900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>452500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>430600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>378500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>407200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>410300</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>11</v>
       </c>
@@ -4114,86 +4216,89 @@
       <c r="AH46" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E47" s="3">
         <v>25800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>25000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>30900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>31700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>30900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>30200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>26300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>26700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>26000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>25500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>27000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>47200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>37300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>36100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>32000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>67800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>58400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>27200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>26900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>26700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>33300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>81400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>79800</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>11</v>
       </c>
@@ -4212,86 +4317,89 @@
       <c r="AH47" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>316700</v>
+      </c>
+      <c r="E48" s="3">
         <v>321800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>317400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>318500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>325800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>323800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>342100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>347400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>340200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>341500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>347400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>332900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>305900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>280000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>246800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>233200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>230000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>226100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>223600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>215100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>214400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>192400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>214400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>217900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>219100</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>11</v>
       </c>
@@ -4310,86 +4418,89 @@
       <c r="AH48" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>435900</v>
+      </c>
+      <c r="E49" s="3">
         <v>442000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>448300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>454400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>459700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>464600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>463700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>469900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>474000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>479300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>508400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>79400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>80000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>80100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>81400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>80300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>56100</v>
-      </c>
-      <c r="T49" s="3">
-        <v>56000</v>
       </c>
       <c r="U49" s="3">
         <v>56000</v>
       </c>
       <c r="V49" s="3">
+        <v>56000</v>
+      </c>
+      <c r="W49" s="3">
         <v>56200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>56400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>56500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>56700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>56500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>21400</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>11</v>
       </c>
@@ -4408,8 +4519,11 @@
       <c r="AH49" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4620,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,86 +4721,89 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E52" s="3">
         <v>42800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>40500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>51800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>49300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>44100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>59200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>54800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>51700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>48900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>57400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>54700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>49300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>98600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>84700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>79100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>31100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>44200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>58800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>46600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>41600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>29000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>18900</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>11</v>
       </c>
@@ -4702,8 +4822,11 @@
       <c r="AH52" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,86 +4923,89 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1412000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1416200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1422700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1384300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1389200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1421000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1441700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1492100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1448900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1530600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1565300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1284900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1234100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1181200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1084100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>979800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>926100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>892600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>851400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>803300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>796900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>747700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>711900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>779700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>749500</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>11</v>
       </c>
@@ -4898,8 +5024,11 @@
       <c r="AH54" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5063,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,86 +5100,87 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>62400</v>
+      </c>
+      <c r="E57" s="3">
         <v>49200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>57300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>45000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>48500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>45300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>55800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>40200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>37600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>40800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>65600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>71800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>60900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>55600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>45300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>39200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>35100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>38200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>32800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>38800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>37700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>22300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>25000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>22900</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>11</v>
       </c>
@@ -5068,58 +5199,61 @@
       <c r="AH57" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E58" s="3">
         <v>7200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7400</v>
-      </c>
-      <c r="F58" s="3">
-        <v>7300</v>
       </c>
       <c r="G58" s="3">
         <v>7300</v>
       </c>
       <c r="H58" s="3">
+        <v>7300</v>
+      </c>
+      <c r="I58" s="3">
         <v>6900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4500</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5140,13 +5274,13 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="3">
         <v>33000</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>11</v>
+      <c r="AB58" s="3">
+        <v>33000</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>11</v>
@@ -5166,86 +5300,89 @@
       <c r="AH58" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="3">
         <v>15100</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" s="3">
         <v>15100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="J59" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
       </c>
       <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
         <v>10300</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>11</v>
+      <c r="N59" s="3">
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q59" s="3">
         <v>24600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>81600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>67400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>72600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>69200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>62600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>55600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>80200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>78900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>66800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>64900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>56100</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>11</v>
       </c>
@@ -5264,86 +5401,89 @@
       <c r="AH59" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>137200</v>
+      </c>
+      <c r="E60" s="3">
         <v>145900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>141100</v>
-      </c>
-      <c r="F60" s="3">
-        <v>120700</v>
       </c>
       <c r="G60" s="3">
         <v>120700</v>
       </c>
       <c r="H60" s="3">
+        <v>120700</v>
+      </c>
+      <c r="I60" s="3">
         <v>112300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>100900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>124000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>105500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>117900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>120200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>134200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>153500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>165300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>137200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>112800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>111800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>104200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>100800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>88400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>119000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>116700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>89100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>122900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>112100</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>11</v>
       </c>
@@ -5362,52 +5502,55 @@
       <c r="AH60" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>297100</v>
+      </c>
+      <c r="E61" s="3">
         <v>298700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>300800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>301400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>327700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>361600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>391300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>413700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>218600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>266000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>266800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>41000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>41400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>38000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>25000</v>
       </c>
       <c r="R61" s="3">
         <v>25000</v>
@@ -5434,7 +5577,7 @@
         <v>25000</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="AA61" s="3">
         <v>0</v>
@@ -5460,86 +5603,89 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E62" s="3">
         <v>6400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>16500</v>
       </c>
       <c r="G62" s="3">
         <v>16500</v>
       </c>
       <c r="H62" s="3">
+        <v>16500</v>
+      </c>
+      <c r="I62" s="3">
         <v>6000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15100</v>
-      </c>
-      <c r="N62" s="3">
-        <v>11400</v>
       </c>
       <c r="O62" s="3">
         <v>11400</v>
       </c>
       <c r="P62" s="3">
+        <v>11400</v>
+      </c>
+      <c r="Q62" s="3">
         <v>2900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>27300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>26200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>28000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>29700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>33300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>33500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>19100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>20900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>21300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>13500</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>11</v>
       </c>
@@ -5558,8 +5704,11 @@
       <c r="AH62" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5805,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5906,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,86 +6007,89 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>446000</v>
+      </c>
+      <c r="E66" s="3">
         <v>459700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>458300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>438500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>465000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>489900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>507300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>553400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>339000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>398900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>429800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>186600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>206300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>214300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>190700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>165000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>163900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>158400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>156700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>147800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>178600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>161900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>136100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>145200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>126500</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>11</v>
       </c>
@@ -5950,8 +6108,11 @@
       <c r="AH66" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6147,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6246,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6347,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6448,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,86 +6549,89 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-52600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-68500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-52000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-60300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-66800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-53600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-38800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-31900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>445300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>463000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>470100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>436800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>371200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>310300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>248300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>183800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>133200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>123000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>97300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>64400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>31200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>208800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>199200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>11</v>
       </c>
@@ -6476,8 +6650,11 @@
       <c r="AH72" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6751,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6852,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,86 +6953,89 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>964300</v>
+      </c>
+      <c r="E76" s="3">
         <v>954700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>962700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>944200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>922700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>929600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>933000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>937300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1108600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1130400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1134200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1097100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1026600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>965600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>893400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>814800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>762200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>734200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>694700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>655400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>618300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>585800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>575800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>634500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>623000</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>11</v>
       </c>
@@ -6868,8 +7054,11 @@
       <c r="AH76" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7155,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46199</v>
+      </c>
+      <c r="E80" s="2">
         <v>46108</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46017</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45835</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45744</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45653</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45380</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45289</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44918</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44827</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44736</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44645</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44554</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44463</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44372</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44099</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43917</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43644</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>39353</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>39262</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>39171</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>39080</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>38989</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-33700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>33300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>65600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>60900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>62000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>64500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>50600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>25600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>32900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>33200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>27700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>8600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>9600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>37000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,92 +7401,93 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E83" s="3">
         <v>9400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>15100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>11900</v>
-      </c>
-      <c r="T83" s="3">
-        <v>12000</v>
       </c>
       <c r="U83" s="3">
         <v>12000</v>
       </c>
       <c r="V83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="W83" s="3">
         <v>12300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>64000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>15500</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>11</v>
       </c>
@@ -7301,8 +7500,11 @@
       <c r="AH83" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7601,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7702,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7803,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7904,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,92 +8005,95 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E89" s="3">
         <v>35700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>45400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>20400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>61600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>20400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>34200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>72600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>46700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>49700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>47500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>53900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>55300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>36600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>37600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>48700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>31400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>38500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>57000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>34900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>25700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>81400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>400</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>11</v>
       </c>
@@ -7889,8 +8106,11 @@
       <c r="AH89" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,92 +8145,93 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-14300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-34400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-31200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-44900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-14300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-14400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-14100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-22000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-18500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-14800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-45600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>11</v>
       </c>
@@ -8023,8 +8244,11 @@
       <c r="AH91" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8345,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,92 +8446,95 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-442500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-25000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-34900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-40600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-14400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-16100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-26800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-8000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-24300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>11</v>
       </c>
@@ -8317,8 +8547,11 @@
       <c r="AH94" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8586,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8397,8 +8631,8 @@
       <c r="P96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8451,8 +8685,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8786,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8887,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,92 +8988,95 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-26500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-44200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-32900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-25900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>7100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-60400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>213900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-11000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-9100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-7500</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-72200</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>82500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>30000</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>11</v>
       </c>
@@ -8843,92 +9089,95 @@
       <c r="AH100" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2200</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-800</v>
       </c>
       <c r="H101" s="3">
         <v>-800</v>
       </c>
       <c r="I101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J101" s="3">
         <v>1300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-6600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE101" s="3" t="s">
         <v>11</v>
       </c>
@@ -8941,92 +9190,95 @@
       <c r="AH101" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E102" s="3">
         <v>12000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>36600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-50100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>14900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-38000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-154700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>16100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>14600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>40800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>23100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>11000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>26100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>25800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>39700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-44200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>116600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>21300</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>11</v>
       </c>
@@ -9037,6 +9289,9 @@
         <v>11</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>11</v>
       </c>
     </row>
